--- a/Sheets/ScheduleData.xlsx
+++ b/Sheets/ScheduleData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D021791-9D44-4842-BB87-FD0F3A844CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149EC374-12FF-465A-A22B-213E6C8B85F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="30" windowWidth="28770" windowHeight="15450" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Rand" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
   <si>
     <t>$$ScheduleData_Rand$$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,9 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>spring_4</t>
-  </si>
-  <si>
     <t>$ScheduleOwner$</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -64,16 +61,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>900 SeedShop 34 5 0/1100 SeedShop 9 17 3/1500 Saloon 42 17 2 abigail_sit_down/2100 SeedShop 1 9 3 abigail_sleep</t>
-  </si>
-  <si>
-    <t>900 SeedShop 11 5 0 \"Strings\\schedules\\Abigail:spring_4.000\"/1230 Hospital 13 14 0 \"Strings\\schedules\\Abigail:spring_4.001\"/1330 Hospital 4 6 1 \"Strings\\schedules\\Abigail:spring_4.002\"/1600 SeedShop 10 5 0/2000 SeedShop 1 9 3 abigail_sleep</t>
-  </si>
-  <si>
     <t>MiniVillagerWoman</t>
   </si>
   <si>
-    <t>900 FarmHouse 5 -5 0/1030 Farm 10 -13 0 death/1500 Mountain 46 23 2 abigail_flute/2000 SeedShop 1 9 3 abigail_sleep</t>
+    <t>Mon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fri</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000 VillagerHouse1 15 -5 0/1300 Town 7 -3 0/1500 Town 20 -10 0/1800 Town 5 -16 0/2000 VillagerHouse1 14 -11 1/2130 VillagerHouse1 13 -5 1 sleep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>630 VillagerHouse1 15 -5 1 sleep/900 VillagerHouse1 13 -5 1 sleep/930 VillagerHouse1 14 -10 0/1000 Town 9 -9 0/1800 Town 19 -17 0/2000 VillagerHouse1 14 -11 1/2130 VillagerHouse1 13 -5 1 sleep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -685,10 +708,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>2</v>
@@ -719,16 +742,16 @@
     <row r="5" spans="1:38">
       <c r="A5" s="12" t="str">
         <f>B5 &amp; "_" &amp; C5</f>
-        <v>MiniVillagerWoman_3</v>
+        <v>MiniVillagerWoman_Mon</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="12">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>6</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -739,17 +762,17 @@
     </row>
     <row r="6" spans="1:38">
       <c r="A6" s="12" t="str">
-        <f t="shared" ref="A6:A7" si="0">B6 &amp; "_" &amp; C6</f>
-        <v>MiniVillagerWoman_5</v>
+        <f t="shared" ref="A6:A11" si="0">B6 &amp; "_" &amp; C6</f>
+        <v>MiniVillagerWoman_Tue</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="12">
         <v>5</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>6</v>
+      <c r="C6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -761,16 +784,16 @@
     <row r="7" spans="1:38">
       <c r="A7" s="12" t="str">
         <f t="shared" si="0"/>
-        <v>MiniVillagerWoman_spring_4</v>
+        <v>MiniVillagerWoman_Wed</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>7</v>
+      <c r="D7" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -780,10 +803,19 @@
       <c r="V7" s="6"/>
     </row>
     <row r="8" spans="1:38">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="A8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>MiniVillagerWoman_Thu</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -792,10 +824,19 @@
       <c r="V8" s="6"/>
     </row>
     <row r="9" spans="1:38">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="A9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>MiniVillagerWoman_Fri</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -804,6 +845,19 @@
       <c r="V9" s="6"/>
     </row>
     <row r="10" spans="1:38">
+      <c r="A10" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>MiniVillagerWoman_Sat</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -812,6 +866,19 @@
       <c r="V10" s="6"/>
     </row>
     <row r="11" spans="1:38">
+      <c r="A11" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>MiniVillagerWoman_Sun</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>13</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>

--- a/Sheets/ScheduleData.xlsx
+++ b/Sheets/ScheduleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149EC374-12FF-465A-A22B-213E6C8B85F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD76B066-136F-47A4-9890-23C3D9BDFC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
@@ -96,7 +96,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>630 VillagerHouse1 15 -5 1 sleep/900 VillagerHouse1 13 -5 1 sleep/930 VillagerHouse1 14 -10 0/1000 Town 9 -9 0/1800 Town 19 -17 0/2000 VillagerHouse1 14 -11 1/2130 VillagerHouse1 13 -5 1 sleep</t>
+    <t>610 VillagerHouse1 13 -7 1 sleep/900 VillagerHouse1 13 -5 1 sleep/930 VillagerHouse1 14 -10 0/1000 Town 9 -9 0/1800 Town 19 -17 0/2000 VillagerHouse1 14 -11 1/2130 VillagerHouse1 13 -5 1 sleep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Sheets/ScheduleData.xlsx
+++ b/Sheets/ScheduleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD76B066-136F-47A4-9890-23C3D9BDFC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81388DA5-A56C-48B1-AEC0-0CD97351951D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Rand" sheetId="6" r:id="rId1"/>
@@ -92,11 +92,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000 VillagerHouse1 15 -5 0/1300 Town 7 -3 0/1500 Town 20 -10 0/1800 Town 5 -16 0/2000 VillagerHouse1 14 -11 1/2130 VillagerHouse1 13 -5 1 sleep</t>
+    <t>610 VillagerHouse1 13 -7 1 sleep/1000 VillagerHouse1 15 -5 0/1300 Town 7 -4 0/1500 Town 20 -12 0/1800 Town 18 -18 0/2000 VillagerHouse1 15 -11 0/2130 VillagerHouse1 13 -7 1 sleep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>610 VillagerHouse1 13 -7 1 sleep/900 VillagerHouse1 13 -5 1 sleep/930 VillagerHouse1 14 -10 0/1000 Town 9 -9 0/1800 Town 19 -17 0/2000 VillagerHouse1 14 -11 1/2130 VillagerHouse1 13 -5 1 sleep</t>
+    <t>610 VillagerHouse1 13 -7 1 sleep/930 VillagerHouse1 15 -11 0/1000 Town 9 -10 0/1800 Town 19 -12 0/2000 VillagerHouse1 15 -11 0/2130 VillagerHouse1 13 -7 1 sleep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Sheets/ScheduleData.xlsx
+++ b/Sheets/ScheduleData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81388DA5-A56C-48B1-AEC0-0CD97351951D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE704542-780D-45CF-8879-D931EF55F328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="Rand" sheetId="6" r:id="rId1"/>
@@ -96,7 +96,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>610 VillagerHouse1 13 -7 1 sleep/930 VillagerHouse1 15 -11 0/1000 Town 9 -10 0/1800 Town 19 -12 0/2000 VillagerHouse1 15 -11 0/2130 VillagerHouse1 13 -7 1 sleep</t>
+    <t>610 VillagerHouse1 13 -8 1 sleep/930 VillagerHouse1 15 -11 0/1000 Town 9 -11 0/1800 Town 19 -12 0/2000 VillagerHouse1 15 -11 0/2130 VillagerHouse1 13 -7 1 sleep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
